--- a/docling-experimentation/data/spreadsheets/example_table.xlsx
+++ b/docling-experimentation/data/spreadsheets/example_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NLP Learning\NLP-Learning\docling-experimentation\data\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14AEFB4-6E47-446C-A75B-4763F198C121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA349C5-1BBC-4CC0-B131-F90C1BC3CBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,15 +148,9 @@
     <t>TRD2023010510977</t>
   </si>
   <si>
-    <t>550260002999.0</t>
-  </si>
-  <si>
     <t>TRD2023010701418</t>
   </si>
   <si>
-    <t>550260003004.0</t>
-  </si>
-  <si>
     <t>TRD2023010704032</t>
   </si>
   <si>
@@ -220,15 +214,9 @@
     <t>TRD2023011906648</t>
   </si>
   <si>
-    <t>550260003265.0</t>
-  </si>
-  <si>
     <t>TDR2023011905515</t>
   </si>
   <si>
-    <t>550260003277.0</t>
-  </si>
-  <si>
     <t>TDR2023012004884</t>
   </si>
   <si>
@@ -1865,6 +1853,18 @@
   </si>
   <si>
     <t>Month</t>
+  </si>
+  <si>
+    <t>5502600032650</t>
+  </si>
+  <si>
+    <t>550260002999</t>
+  </si>
+  <si>
+    <t>550260003004</t>
+  </si>
+  <si>
+    <t>550260003277</t>
   </si>
 </sst>
 </file>
@@ -1921,11 +1921,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2231,35 +2232,36 @@
   <dimension ref="A1:F302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2">
@@ -2279,7 +2281,7 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3">
@@ -2299,7 +2301,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4">
@@ -2319,7 +2321,7 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5">
@@ -2339,7 +2341,7 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C6">
@@ -2359,7 +2361,7 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7">
@@ -2379,7 +2381,7 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C8">
@@ -2399,7 +2401,7 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9">
@@ -2419,7 +2421,7 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C10">
@@ -2439,7 +2441,7 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C11">
@@ -2459,7 +2461,7 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C12">
@@ -2479,7 +2481,7 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C13">
@@ -2499,7 +2501,7 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C14">
@@ -2519,7 +2521,7 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C15">
@@ -2539,7 +2541,7 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C16">
@@ -2559,7 +2561,7 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C17">
@@ -2579,7 +2581,7 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C18">
@@ -2599,7 +2601,7 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C19">
@@ -2619,7 +2621,7 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C20">
@@ -2639,7 +2641,7 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C21">
@@ -2659,8 +2661,8 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>42</v>
+      <c r="B22" s="2" t="s">
+        <v>612</v>
       </c>
       <c r="C22">
         <v>140000</v>
@@ -2669,7 +2671,7 @@
         <v>137200</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
         <v>3</v>
@@ -2679,8 +2681,8 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>44</v>
+      <c r="B23" s="2" t="s">
+        <v>613</v>
       </c>
       <c r="C23">
         <v>108200</v>
@@ -2689,7 +2691,7 @@
         <v>106036</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
         <v>3</v>
@@ -2699,8 +2701,8 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>46</v>
+      <c r="B24" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C24">
         <v>250440</v>
@@ -2709,7 +2711,7 @@
         <v>245431.2</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>3</v>
@@ -2719,8 +2721,8 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>48</v>
+      <c r="B25" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C25">
         <v>303000</v>
@@ -2729,7 +2731,7 @@
         <v>296940</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s">
         <v>3</v>
@@ -2739,8 +2741,8 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>50</v>
+      <c r="B26" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="C26">
         <v>64000</v>
@@ -2749,7 +2751,7 @@
         <v>62720</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
         <v>3</v>
@@ -2759,8 +2761,8 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>52</v>
+      <c r="B27" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C27">
         <v>54000</v>
@@ -2769,7 +2771,7 @@
         <v>52920</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
         <v>3</v>
@@ -2779,8 +2781,8 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>54</v>
+      <c r="B28" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C28">
         <v>136000</v>
@@ -2789,7 +2791,7 @@
         <v>133280</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
         <v>3</v>
@@ -2799,8 +2801,8 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>56</v>
+      <c r="B29" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C29">
         <v>190000</v>
@@ -2809,7 +2811,7 @@
         <v>186200</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
         <v>3</v>
@@ -2819,8 +2821,8 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>58</v>
+      <c r="B30" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C30">
         <v>46000</v>
@@ -2829,7 +2831,7 @@
         <v>45080</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
         <v>3</v>
@@ -2839,8 +2841,8 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>60</v>
+      <c r="B31" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C31">
         <v>303000</v>
@@ -2849,7 +2851,7 @@
         <v>296940</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
         <v>3</v>
@@ -2859,8 +2861,8 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>62</v>
+      <c r="B32" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C32">
         <v>51000</v>
@@ -2869,7 +2871,7 @@
         <v>49980</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F32" t="s">
         <v>3</v>
@@ -2879,8 +2881,8 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
-        <v>64</v>
+      <c r="B33" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C33">
         <v>181000</v>
@@ -2889,7 +2891,7 @@
         <v>177380</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
         <v>3</v>
@@ -2899,8 +2901,8 @@
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>66</v>
+      <c r="B34" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="C34">
         <v>64000</v>
@@ -2909,7 +2911,7 @@
         <v>62720</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
         <v>3</v>
@@ -2919,8 +2921,8 @@
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>68</v>
+      <c r="B35" s="2" t="s">
+        <v>614</v>
       </c>
       <c r="C35">
         <v>54000</v>
@@ -2929,7 +2931,7 @@
         <v>52920</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
         <v>3</v>
@@ -2939,8 +2941,8 @@
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
-        <v>70</v>
+      <c r="B36" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="C36">
         <v>150000</v>
@@ -2949,7 +2951,7 @@
         <v>147000</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F36" t="s">
         <v>3</v>
@@ -2959,8 +2961,8 @@
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
+      <c r="B37" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C37">
         <v>250000</v>
@@ -2969,7 +2971,7 @@
         <v>245000</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F37" t="s">
         <v>3</v>
@@ -2979,8 +2981,8 @@
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
-        <v>74</v>
+      <c r="B38" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C38">
         <v>125000</v>
@@ -2989,7 +2991,7 @@
         <v>122500</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
         <v>3</v>
@@ -2999,8 +3001,8 @@
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
-        <v>76</v>
+      <c r="B39" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C39">
         <v>360000</v>
@@ -3009,7 +3011,7 @@
         <v>352800</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
         <v>3</v>
@@ -3019,8 +3021,8 @@
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
-        <v>78</v>
+      <c r="B40" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C40">
         <v>250000</v>
@@ -3029,7 +3031,7 @@
         <v>245000</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
         <v>3</v>
@@ -3039,8 +3041,8 @@
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
-        <v>80</v>
+      <c r="B41" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C41">
         <v>33000</v>
@@ -3049,18 +3051,18 @@
         <v>32340</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
-        <v>83</v>
+      <c r="B42" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C42">
         <v>228000</v>
@@ -3069,18 +3071,18 @@
         <v>223440</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
-        <v>85</v>
+      <c r="B43" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C43">
         <v>34000</v>
@@ -3089,18 +3091,18 @@
         <v>33320</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
-        <v>87</v>
+      <c r="B44" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C44">
         <v>100000</v>
@@ -3109,18 +3111,18 @@
         <v>98000</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
-        <v>89</v>
+      <c r="B45" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C45">
         <v>60000</v>
@@ -3129,18 +3131,18 @@
         <v>58800</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
-        <v>91</v>
+      <c r="B46" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C46">
         <v>70000</v>
@@ -3149,18 +3151,18 @@
         <v>68600</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
-        <v>93</v>
+      <c r="B47" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C47">
         <v>54000</v>
@@ -3169,18 +3171,18 @@
         <v>52920</v>
       </c>
       <c r="E47" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
-        <v>95</v>
+      <c r="B48" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C48">
         <v>22800</v>
@@ -3189,18 +3191,18 @@
         <v>22344</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
-        <v>97</v>
+      <c r="B49" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C49">
         <v>80000</v>
@@ -3209,18 +3211,18 @@
         <v>78400</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
-        <v>99</v>
+      <c r="B50" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C50">
         <v>100000</v>
@@ -3229,18 +3231,18 @@
         <v>98000</v>
       </c>
       <c r="E50" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
-        <v>101</v>
+      <c r="B51" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C51">
         <v>34000</v>
@@ -3249,18 +3251,18 @@
         <v>33320</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
-        <v>103</v>
+      <c r="B52" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C52">
         <v>60000</v>
@@ -3269,18 +3271,18 @@
         <v>58800</v>
       </c>
       <c r="E52" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" t="s">
-        <v>105</v>
+      <c r="B53" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C53">
         <v>70000</v>
@@ -3289,18 +3291,18 @@
         <v>68600</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F53" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54" t="s">
-        <v>107</v>
+      <c r="B54" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C54">
         <v>80110</v>
@@ -3309,18 +3311,18 @@
         <v>78507.8</v>
       </c>
       <c r="E54" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55" t="s">
-        <v>109</v>
+      <c r="B55" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C55">
         <v>34000</v>
@@ -3329,18 +3331,18 @@
         <v>33320</v>
       </c>
       <c r="E55" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F55" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
-        <v>111</v>
+      <c r="B56" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C56">
         <v>56000</v>
@@ -3349,18 +3351,18 @@
         <v>54880</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57" t="s">
-        <v>113</v>
+      <c r="B57" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C57">
         <v>64000</v>
@@ -3369,18 +3371,18 @@
         <v>62720</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F57" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58" t="s">
-        <v>115</v>
+      <c r="B58" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C58">
         <v>100000</v>
@@ -3389,18 +3391,18 @@
         <v>98000</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F58" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
-        <v>117</v>
+      <c r="B59" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="C59">
         <v>132000</v>
@@ -3409,18 +3411,18 @@
         <v>129360</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60" t="s">
-        <v>119</v>
+      <c r="B60" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C60">
         <v>110160</v>
@@ -3429,18 +3431,18 @@
         <v>107956.8</v>
       </c>
       <c r="E60" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F60" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
-        <v>121</v>
+      <c r="B61" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="C61">
         <v>44000</v>
@@ -3449,18 +3451,18 @@
         <v>43120</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F61" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62" t="s">
-        <v>123</v>
+      <c r="B62" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C62">
         <v>37000</v>
@@ -3469,18 +3471,18 @@
         <v>36260</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
-        <v>125</v>
+      <c r="B63" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C63">
         <v>109000</v>
@@ -3489,18 +3491,18 @@
         <v>106820</v>
       </c>
       <c r="E63" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F63" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
-        <v>127</v>
+      <c r="B64" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C64">
         <v>17000</v>
@@ -3509,18 +3511,18 @@
         <v>16660</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F64" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65" t="s">
-        <v>129</v>
+      <c r="B65" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C65">
         <v>35054</v>
@@ -3529,18 +3531,18 @@
         <v>34352.92</v>
       </c>
       <c r="E65" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F65" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66" t="s">
-        <v>131</v>
+      <c r="B66" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C66">
         <v>140000</v>
@@ -3549,18 +3551,18 @@
         <v>137200</v>
       </c>
       <c r="E66" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67" t="s">
-        <v>134</v>
+      <c r="B67" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="C67">
         <v>300000</v>
@@ -3569,18 +3571,18 @@
         <v>294000</v>
       </c>
       <c r="E67" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68" t="s">
-        <v>136</v>
+      <c r="B68" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C68">
         <v>43000</v>
@@ -3589,18 +3591,18 @@
         <v>42140</v>
       </c>
       <c r="E68" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F68" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69" t="s">
-        <v>138</v>
+      <c r="B69" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C69">
         <v>60000</v>
@@ -3609,18 +3611,18 @@
         <v>58800</v>
       </c>
       <c r="E69" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F69" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70" t="s">
-        <v>140</v>
+      <c r="B70" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="C70">
         <v>54000</v>
@@ -3629,18 +3631,18 @@
         <v>52920</v>
       </c>
       <c r="E70" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F70" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
-      <c r="B71" t="s">
-        <v>142</v>
+      <c r="B71" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="C71">
         <v>59000</v>
@@ -3649,18 +3651,18 @@
         <v>57820</v>
       </c>
       <c r="E71" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
-      <c r="B72" t="s">
-        <v>144</v>
+      <c r="B72" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C72">
         <v>75000</v>
@@ -3669,18 +3671,18 @@
         <v>73500</v>
       </c>
       <c r="E72" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
-      <c r="B73" t="s">
-        <v>146</v>
+      <c r="B73" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="C73">
         <v>54000</v>
@@ -3689,18 +3691,18 @@
         <v>52920</v>
       </c>
       <c r="E73" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
-      <c r="B74" t="s">
-        <v>148</v>
+      <c r="B74" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="C74">
         <v>170300</v>
@@ -3709,18 +3711,18 @@
         <v>166894</v>
       </c>
       <c r="E74" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>73</v>
       </c>
-      <c r="B75" t="s">
-        <v>150</v>
+      <c r="B75" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C75">
         <v>172000</v>
@@ -3729,18 +3731,18 @@
         <v>168560</v>
       </c>
       <c r="E75" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B76" t="s">
-        <v>152</v>
+      <c r="B76" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="C76">
         <v>64000</v>
@@ -3749,18 +3751,18 @@
         <v>62720</v>
       </c>
       <c r="E76" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77" t="s">
-        <v>154</v>
+      <c r="B77" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="C77">
         <v>70000</v>
@@ -3769,18 +3771,18 @@
         <v>68600</v>
       </c>
       <c r="E77" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F77" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>76</v>
       </c>
-      <c r="B78" t="s">
-        <v>156</v>
+      <c r="B78" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C78">
         <v>79000</v>
@@ -3789,18 +3791,18 @@
         <v>77420</v>
       </c>
       <c r="E78" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B79" t="s">
-        <v>158</v>
+      <c r="B79" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C79">
         <v>100000</v>
@@ -3809,18 +3811,18 @@
         <v>98000</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F79" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B80" t="s">
-        <v>160</v>
+      <c r="B80" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C80">
         <v>200000</v>
@@ -3829,18 +3831,18 @@
         <v>196000</v>
       </c>
       <c r="E80" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F80" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B81" t="s">
-        <v>162</v>
+      <c r="B81" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="C81">
         <v>8000</v>
@@ -3849,18 +3851,18 @@
         <v>7840</v>
       </c>
       <c r="E81" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F81" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B82" t="s">
-        <v>164</v>
+      <c r="B82" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="C82">
         <v>79000</v>
@@ -3869,18 +3871,18 @@
         <v>77420</v>
       </c>
       <c r="E82" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F82" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
-      <c r="B83" t="s">
-        <v>166</v>
+      <c r="B83" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C83">
         <v>100000</v>
@@ -3889,18 +3891,18 @@
         <v>98000</v>
       </c>
       <c r="E83" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F83" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="B84" t="s">
-        <v>168</v>
+      <c r="B84" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C84">
         <v>52000</v>
@@ -3909,18 +3911,18 @@
         <v>50960</v>
       </c>
       <c r="E84" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F84" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B85" t="s">
-        <v>170</v>
+      <c r="B85" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="C85">
         <v>79000</v>
@@ -3929,18 +3931,18 @@
         <v>77420</v>
       </c>
       <c r="E85" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F85" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B86" t="s">
-        <v>172</v>
+      <c r="B86" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="C86">
         <v>168000</v>
@@ -3949,18 +3951,18 @@
         <v>164640</v>
       </c>
       <c r="E86" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F86" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
-      <c r="B87" t="s">
-        <v>174</v>
+      <c r="B87" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C87">
         <v>50000</v>
@@ -3969,18 +3971,18 @@
         <v>49000</v>
       </c>
       <c r="E87" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F87" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>86</v>
       </c>
-      <c r="B88" t="s">
-        <v>176</v>
+      <c r="B88" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="C88">
         <v>100000</v>
@@ -3989,18 +3991,18 @@
         <v>98000</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F88" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89" t="s">
-        <v>178</v>
+      <c r="B89" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="C89">
         <v>60000</v>
@@ -4009,18 +4011,18 @@
         <v>58800</v>
       </c>
       <c r="E89" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F89" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
-      <c r="B90" t="s">
-        <v>180</v>
+      <c r="B90" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C90">
         <v>98000</v>
@@ -4029,18 +4031,18 @@
         <v>96040</v>
       </c>
       <c r="E90" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F90" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>89</v>
       </c>
-      <c r="B91" t="s">
-        <v>183</v>
+      <c r="B91" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="C91">
         <v>29900</v>
@@ -4049,18 +4051,18 @@
         <v>29302</v>
       </c>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F91" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B92" t="s">
-        <v>185</v>
+      <c r="B92" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C92">
         <v>155000</v>
@@ -4069,18 +4071,18 @@
         <v>151900</v>
       </c>
       <c r="E92" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F92" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B93" t="s">
-        <v>187</v>
+      <c r="B93" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="C93">
         <v>79000</v>
@@ -4089,18 +4091,18 @@
         <v>77420</v>
       </c>
       <c r="E93" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
-      <c r="B94" t="s">
-        <v>189</v>
+      <c r="B94" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="C94">
         <v>490930</v>
@@ -4109,18 +4111,18 @@
         <v>481111.4</v>
       </c>
       <c r="E94" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F94" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B95" t="s">
-        <v>191</v>
+      <c r="B95" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="C95">
         <v>112000</v>
@@ -4129,18 +4131,18 @@
         <v>109760</v>
       </c>
       <c r="E95" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F95" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B96" t="s">
-        <v>193</v>
+      <c r="B96" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="C96">
         <v>174000</v>
@@ -4149,18 +4151,18 @@
         <v>170520</v>
       </c>
       <c r="E96" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F96" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
-      <c r="B97" t="s">
-        <v>195</v>
+      <c r="B97" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C97">
         <v>40000</v>
@@ -4169,18 +4171,18 @@
         <v>39200</v>
       </c>
       <c r="E97" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F97" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
-      <c r="B98" t="s">
-        <v>197</v>
+      <c r="B98" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="C98">
         <v>54000</v>
@@ -4189,18 +4191,18 @@
         <v>52920</v>
       </c>
       <c r="E98" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F98" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B99" t="s">
-        <v>199</v>
+      <c r="B99" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C99">
         <v>28000</v>
@@ -4209,18 +4211,18 @@
         <v>27440</v>
       </c>
       <c r="E99" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F99" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B100" t="s">
-        <v>201</v>
+      <c r="B100" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C100">
         <v>287000</v>
@@ -4229,18 +4231,18 @@
         <v>281260</v>
       </c>
       <c r="E100" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F100" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
-      <c r="B101" t="s">
-        <v>203</v>
+      <c r="B101" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C101">
         <v>13000</v>
@@ -4249,18 +4251,18 @@
         <v>12740</v>
       </c>
       <c r="E101" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F101" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
-        <v>205</v>
+      <c r="B102" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C102">
         <v>82150</v>
@@ -4269,18 +4271,18 @@
         <v>80507</v>
       </c>
       <c r="E102" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F102" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
-      <c r="B103" t="s">
-        <v>207</v>
+      <c r="B103" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C103">
         <v>174000</v>
@@ -4289,18 +4291,18 @@
         <v>170520</v>
       </c>
       <c r="E103" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
-        <v>209</v>
+      <c r="B104" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="C104">
         <v>100000</v>
@@ -4309,18 +4311,18 @@
         <v>98000</v>
       </c>
       <c r="E104" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F104" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
-      <c r="B105" t="s">
-        <v>211</v>
+      <c r="B105" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C105">
         <v>40000</v>
@@ -4329,18 +4331,18 @@
         <v>39200</v>
       </c>
       <c r="E105" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F105" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
-      <c r="B106" t="s">
-        <v>213</v>
+      <c r="B106" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="C106">
         <v>54000</v>
@@ -4349,18 +4351,18 @@
         <v>52920</v>
       </c>
       <c r="E106" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F106" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
-      <c r="B107" t="s">
-        <v>215</v>
+      <c r="B107" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="C107">
         <v>59000</v>
@@ -4369,18 +4371,18 @@
         <v>57820</v>
       </c>
       <c r="E107" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F107" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
-      <c r="B108" t="s">
-        <v>217</v>
+      <c r="B108" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="C108">
         <v>67000</v>
@@ -4389,18 +4391,18 @@
         <v>65660</v>
       </c>
       <c r="E108" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
-      <c r="B109" t="s">
-        <v>219</v>
+      <c r="B109" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="C109">
         <v>40000</v>
@@ -4409,18 +4411,18 @@
         <v>39200</v>
       </c>
       <c r="E109" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F109" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
-      <c r="B110" t="s">
-        <v>221</v>
+      <c r="B110" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="C110">
         <v>100000</v>
@@ -4429,18 +4431,18 @@
         <v>98000</v>
       </c>
       <c r="E110" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F110" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
-      <c r="B111" t="s">
-        <v>223</v>
+      <c r="B111" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="C111">
         <v>100000</v>
@@ -4449,18 +4451,18 @@
         <v>98000</v>
       </c>
       <c r="E111" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
-      <c r="B112" t="s">
-        <v>225</v>
+      <c r="B112" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="C112">
         <v>94000</v>
@@ -4469,18 +4471,18 @@
         <v>92120</v>
       </c>
       <c r="E112" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F112" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
-      <c r="B113" t="s">
-        <v>227</v>
+      <c r="B113" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="C113">
         <v>109000</v>
@@ -4489,18 +4491,18 @@
         <v>106820</v>
       </c>
       <c r="E113" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F113" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
-      <c r="B114" t="s">
-        <v>229</v>
+      <c r="B114" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C114">
         <v>26000</v>
@@ -4509,18 +4511,18 @@
         <v>25480</v>
       </c>
       <c r="E114" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F114" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
-      <c r="B115" t="s">
-        <v>231</v>
+      <c r="B115" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="C115">
         <v>108000</v>
@@ -4529,18 +4531,18 @@
         <v>105840</v>
       </c>
       <c r="E115" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F115" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
-      <c r="B116" t="s">
-        <v>233</v>
+      <c r="B116" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="C116">
         <v>139000</v>
@@ -4549,18 +4551,18 @@
         <v>136220</v>
       </c>
       <c r="E116" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F116" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
-      <c r="B117" t="s">
-        <v>235</v>
+      <c r="B117" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="C117">
         <v>54000</v>
@@ -4569,18 +4571,18 @@
         <v>52920</v>
       </c>
       <c r="E117" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F117" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
-      <c r="B118" t="s">
-        <v>237</v>
+      <c r="B118" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="C118">
         <v>49000</v>
@@ -4589,18 +4591,18 @@
         <v>48020</v>
       </c>
       <c r="E118" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
-      <c r="B119" t="s">
-        <v>239</v>
+      <c r="B119" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="C119">
         <v>46000</v>
@@ -4609,18 +4611,18 @@
         <v>45080</v>
       </c>
       <c r="E119" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
-      <c r="B120" t="s">
-        <v>242</v>
+      <c r="B120" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="C120">
         <v>59000</v>
@@ -4629,18 +4631,18 @@
         <v>57820</v>
       </c>
       <c r="E120" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F120" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
-      <c r="B121" t="s">
-        <v>244</v>
+      <c r="B121" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="C121">
         <v>64000</v>
@@ -4649,18 +4651,18 @@
         <v>62720</v>
       </c>
       <c r="E121" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
-      <c r="B122" t="s">
-        <v>246</v>
+      <c r="B122" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="C122">
         <v>16000</v>
@@ -4669,18 +4671,18 @@
         <v>15680</v>
       </c>
       <c r="E122" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F122" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
-      <c r="B123" t="s">
-        <v>248</v>
+      <c r="B123" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="C123">
         <v>64000</v>
@@ -4689,18 +4691,18 @@
         <v>62720</v>
       </c>
       <c r="E123" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F123" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
-      <c r="B124" t="s">
-        <v>250</v>
+      <c r="B124" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="C124">
         <v>119000</v>
@@ -4709,18 +4711,18 @@
         <v>116620</v>
       </c>
       <c r="E124" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F124" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
-      <c r="B125" t="s">
-        <v>252</v>
+      <c r="B125" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="C125">
         <v>44000</v>
@@ -4729,18 +4731,18 @@
         <v>43120</v>
       </c>
       <c r="E125" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F125" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
-      <c r="B126" t="s">
-        <v>254</v>
+      <c r="B126" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="C126">
         <v>64000</v>
@@ -4749,18 +4751,18 @@
         <v>62720</v>
       </c>
       <c r="E126" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F126" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
-      <c r="B127" t="s">
-        <v>256</v>
+      <c r="B127" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="C127">
         <v>59000</v>
@@ -4769,18 +4771,18 @@
         <v>57820</v>
       </c>
       <c r="E127" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F127" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
-      <c r="B128" t="s">
-        <v>258</v>
+      <c r="B128" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="C128">
         <v>64000</v>
@@ -4789,18 +4791,18 @@
         <v>62720</v>
       </c>
       <c r="E128" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F128" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
-      <c r="B129" t="s">
-        <v>260</v>
+      <c r="B129" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="C129">
         <v>80000</v>
@@ -4809,18 +4811,18 @@
         <v>78400</v>
       </c>
       <c r="E129" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F129" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
-      <c r="B130" t="s">
-        <v>262</v>
+      <c r="B130" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="C130">
         <v>300000</v>
@@ -4829,18 +4831,18 @@
         <v>294000</v>
       </c>
       <c r="E130" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F130" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
-      <c r="B131" t="s">
-        <v>264</v>
+      <c r="B131" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C131">
         <v>124000</v>
@@ -4849,18 +4851,18 @@
         <v>121520</v>
       </c>
       <c r="E131" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F131" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
-      <c r="B132" t="s">
-        <v>266</v>
+      <c r="B132" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="C132">
         <v>94000</v>
@@ -4869,18 +4871,18 @@
         <v>92120</v>
       </c>
       <c r="E132" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F132" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
-      <c r="B133" t="s">
-        <v>268</v>
+      <c r="B133" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="C133">
         <v>94000</v>
@@ -4889,18 +4891,18 @@
         <v>92120</v>
       </c>
       <c r="E133" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F133" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
-      <c r="B134" t="s">
-        <v>270</v>
+      <c r="B134" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="C134">
         <v>350000</v>
@@ -4909,18 +4911,18 @@
         <v>343000</v>
       </c>
       <c r="E134" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F134" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
-      <c r="B135" t="s">
-        <v>272</v>
+      <c r="B135" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="C135">
         <v>50000</v>
@@ -4929,18 +4931,18 @@
         <v>49000</v>
       </c>
       <c r="E135" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F135" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
-      <c r="B136" t="s">
-        <v>274</v>
+      <c r="B136" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="C136">
         <v>70000</v>
@@ -4949,18 +4951,18 @@
         <v>68600</v>
       </c>
       <c r="E136" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F136" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
-      <c r="B137" t="s">
-        <v>276</v>
+      <c r="B137" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="C137">
         <v>100000</v>
@@ -4969,18 +4971,18 @@
         <v>98000</v>
       </c>
       <c r="E137" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F137" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
-      <c r="B138" t="s">
-        <v>278</v>
+      <c r="B138" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="C138">
         <v>49000</v>
@@ -4989,18 +4991,18 @@
         <v>48020</v>
       </c>
       <c r="E138" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F138" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>137</v>
       </c>
-      <c r="B139" t="s">
-        <v>280</v>
+      <c r="B139" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="C139">
         <v>100000</v>
@@ -5009,18 +5011,18 @@
         <v>98000</v>
       </c>
       <c r="E139" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F139" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>138</v>
       </c>
-      <c r="B140" t="s">
-        <v>282</v>
+      <c r="B140" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C140">
         <v>100000</v>
@@ -5029,18 +5031,18 @@
         <v>98000</v>
       </c>
       <c r="E140" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F140" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>139</v>
       </c>
-      <c r="B141" t="s">
-        <v>284</v>
+      <c r="B141" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="C141">
         <v>100000</v>
@@ -5049,18 +5051,18 @@
         <v>98000</v>
       </c>
       <c r="E141" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F141" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>140</v>
       </c>
-      <c r="B142" t="s">
-        <v>286</v>
+      <c r="B142" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="C142">
         <v>108000</v>
@@ -5069,18 +5071,18 @@
         <v>105840</v>
       </c>
       <c r="E142" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F142" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>141</v>
       </c>
-      <c r="B143" t="s">
-        <v>288</v>
+      <c r="B143" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="C143">
         <v>98000</v>
@@ -5089,18 +5091,18 @@
         <v>96040</v>
       </c>
       <c r="E143" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F143" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>142</v>
       </c>
-      <c r="B144" t="s">
-        <v>290</v>
+      <c r="B144" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="C144">
         <v>104000</v>
@@ -5109,18 +5111,18 @@
         <v>101920</v>
       </c>
       <c r="E144" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F144" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>143</v>
       </c>
-      <c r="B145" t="s">
-        <v>292</v>
+      <c r="B145" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C145">
         <v>104000</v>
@@ -5129,18 +5131,18 @@
         <v>101920</v>
       </c>
       <c r="E145" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F145" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>144</v>
       </c>
-      <c r="B146" t="s">
-        <v>294</v>
+      <c r="B146" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="C146">
         <v>103000</v>
@@ -5149,18 +5151,18 @@
         <v>100940</v>
       </c>
       <c r="E146" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F146" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>145</v>
       </c>
-      <c r="B147" t="s">
-        <v>296</v>
+      <c r="B147" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="C147">
         <v>108000</v>
@@ -5169,18 +5171,18 @@
         <v>105840</v>
       </c>
       <c r="E147" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F147" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>146</v>
       </c>
-      <c r="B148" t="s">
-        <v>298</v>
+      <c r="B148" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="C148">
         <v>95000</v>
@@ -5189,18 +5191,18 @@
         <v>93100</v>
       </c>
       <c r="E148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F148" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>147</v>
       </c>
-      <c r="B149" t="s">
-        <v>300</v>
+      <c r="B149" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="C149">
         <v>100000</v>
@@ -5209,18 +5211,18 @@
         <v>98000</v>
       </c>
       <c r="E149" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F149" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>148</v>
       </c>
-      <c r="B150" t="s">
-        <v>302</v>
+      <c r="B150" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="C150">
         <v>100000</v>
@@ -5229,18 +5231,18 @@
         <v>98000</v>
       </c>
       <c r="E150" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F150" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>149</v>
       </c>
-      <c r="B151" t="s">
-        <v>304</v>
+      <c r="B151" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="C151">
         <v>100000</v>
@@ -5249,18 +5251,18 @@
         <v>98000</v>
       </c>
       <c r="E151" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F151" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>150</v>
       </c>
-      <c r="B152" t="s">
-        <v>306</v>
+      <c r="B152" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C152">
         <v>103000</v>
@@ -5269,18 +5271,18 @@
         <v>100940</v>
       </c>
       <c r="E152" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F152" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>151</v>
       </c>
-      <c r="B153" t="s">
-        <v>308</v>
+      <c r="B153" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="C153">
         <v>102000</v>
@@ -5289,18 +5291,18 @@
         <v>99960</v>
       </c>
       <c r="E153" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F153" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>152</v>
       </c>
-      <c r="B154" t="s">
-        <v>310</v>
+      <c r="B154" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="C154">
         <v>34000</v>
@@ -5309,18 +5311,18 @@
         <v>33320</v>
       </c>
       <c r="E154" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F154" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>153</v>
       </c>
-      <c r="B155" t="s">
-        <v>312</v>
+      <c r="B155" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="C155">
         <v>150000</v>
@@ -5329,18 +5331,18 @@
         <v>147000</v>
       </c>
       <c r="E155" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F155" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>154</v>
       </c>
-      <c r="B156" t="s">
-        <v>314</v>
+      <c r="B156" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="C156">
         <v>100000</v>
@@ -5349,18 +5351,18 @@
         <v>98000</v>
       </c>
       <c r="E156" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F156" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>155</v>
       </c>
-      <c r="B157" t="s">
-        <v>316</v>
+      <c r="B157" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="C157">
         <v>63000</v>
@@ -5369,18 +5371,18 @@
         <v>61740</v>
       </c>
       <c r="E157" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F157" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>156</v>
       </c>
-      <c r="B158" t="s">
-        <v>318</v>
+      <c r="B158" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="C158">
         <v>100000</v>
@@ -5389,18 +5391,18 @@
         <v>98000</v>
       </c>
       <c r="E158" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F158" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>157</v>
       </c>
-      <c r="B159" t="s">
-        <v>320</v>
+      <c r="B159" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="C159">
         <v>52000</v>
@@ -5409,18 +5411,18 @@
         <v>50960</v>
       </c>
       <c r="E159" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F159" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>158</v>
       </c>
-      <c r="B160" t="s">
-        <v>322</v>
+      <c r="B160" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="C160">
         <v>95000</v>
@@ -5429,18 +5431,18 @@
         <v>93100</v>
       </c>
       <c r="E160" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F160" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>159</v>
       </c>
-      <c r="B161" t="s">
-        <v>324</v>
+      <c r="B161" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="C161">
         <v>49000</v>
@@ -5449,18 +5451,18 @@
         <v>48020</v>
       </c>
       <c r="E161" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F161" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>160</v>
       </c>
-      <c r="B162" t="s">
-        <v>326</v>
+      <c r="B162" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="C162">
         <v>100000</v>
@@ -5469,18 +5471,18 @@
         <v>98000</v>
       </c>
       <c r="E162" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F162" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>161</v>
       </c>
-      <c r="B163" t="s">
-        <v>328</v>
+      <c r="B163" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="C163">
         <v>65000</v>
@@ -5489,18 +5491,18 @@
         <v>63700</v>
       </c>
       <c r="E163" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F163" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>162</v>
       </c>
-      <c r="B164" t="s">
-        <v>330</v>
+      <c r="B164" s="2" t="s">
+        <v>326</v>
       </c>
       <c r="C164">
         <v>16000</v>
@@ -5509,18 +5511,18 @@
         <v>15680</v>
       </c>
       <c r="E164" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F164" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>163</v>
       </c>
-      <c r="B165" t="s">
-        <v>332</v>
+      <c r="B165" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="C165">
         <v>108000</v>
@@ -5529,18 +5531,18 @@
         <v>105840</v>
       </c>
       <c r="E165" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F165" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>164</v>
       </c>
-      <c r="B166" t="s">
-        <v>334</v>
+      <c r="B166" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="C166">
         <v>100000</v>
@@ -5549,18 +5551,18 @@
         <v>98000</v>
       </c>
       <c r="E166" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F166" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>165</v>
       </c>
-      <c r="B167" t="s">
-        <v>337</v>
+      <c r="B167" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C167">
         <v>52000</v>
@@ -5569,18 +5571,18 @@
         <v>50960</v>
       </c>
       <c r="E167" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F167" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>166</v>
       </c>
-      <c r="B168" t="s">
-        <v>339</v>
+      <c r="B168" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C168">
         <v>102000</v>
@@ -5589,18 +5591,18 @@
         <v>99960</v>
       </c>
       <c r="E168" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F168" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>167</v>
       </c>
-      <c r="B169" t="s">
-        <v>341</v>
+      <c r="B169" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C169">
         <v>60000</v>
@@ -5609,18 +5611,18 @@
         <v>58800</v>
       </c>
       <c r="E169" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F169" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>168</v>
       </c>
-      <c r="B170" t="s">
-        <v>343</v>
+      <c r="B170" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="C170">
         <v>99000</v>
@@ -5629,18 +5631,18 @@
         <v>97020</v>
       </c>
       <c r="E170" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F170" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>169</v>
       </c>
-      <c r="B171" t="s">
-        <v>345</v>
+      <c r="B171" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="C171">
         <v>34000</v>
@@ -5649,18 +5651,18 @@
         <v>33320</v>
       </c>
       <c r="E171" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F171" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>170</v>
       </c>
-      <c r="B172" t="s">
-        <v>347</v>
+      <c r="B172" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C172">
         <v>220000</v>
@@ -5669,18 +5671,18 @@
         <v>215600</v>
       </c>
       <c r="E172" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F172" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>171</v>
       </c>
-      <c r="B173" t="s">
-        <v>349</v>
+      <c r="B173" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C173">
         <v>200000</v>
@@ -5689,18 +5691,18 @@
         <v>196000</v>
       </c>
       <c r="E173" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F173" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>172</v>
       </c>
-      <c r="B174" t="s">
-        <v>351</v>
+      <c r="B174" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="C174">
         <v>34000</v>
@@ -5709,18 +5711,18 @@
         <v>33320</v>
       </c>
       <c r="E174" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F174" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>173</v>
       </c>
-      <c r="B175" t="s">
-        <v>353</v>
+      <c r="B175" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="C175">
         <v>100000</v>
@@ -5729,18 +5731,18 @@
         <v>98000</v>
       </c>
       <c r="E175" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F175" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>174</v>
       </c>
-      <c r="B176" t="s">
-        <v>355</v>
+      <c r="B176" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="C176">
         <v>100000</v>
@@ -5749,18 +5751,18 @@
         <v>98000</v>
       </c>
       <c r="E176" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F176" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>175</v>
       </c>
-      <c r="B177" t="s">
-        <v>357</v>
+      <c r="B177" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="C177">
         <v>100000</v>
@@ -5769,18 +5771,18 @@
         <v>98000</v>
       </c>
       <c r="E177" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F177" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>176</v>
       </c>
-      <c r="B178" t="s">
-        <v>359</v>
+      <c r="B178" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="C178">
         <v>100000</v>
@@ -5789,18 +5791,18 @@
         <v>98000</v>
       </c>
       <c r="E178" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F178" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>177</v>
       </c>
-      <c r="B179" t="s">
-        <v>361</v>
+      <c r="B179" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="C179">
         <v>58000</v>
@@ -5809,18 +5811,18 @@
         <v>56840</v>
       </c>
       <c r="E179" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F179" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>178</v>
       </c>
-      <c r="B180" t="s">
-        <v>363</v>
+      <c r="B180" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="C180">
         <v>100000</v>
@@ -5829,18 +5831,18 @@
         <v>98000</v>
       </c>
       <c r="E180" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F180" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>179</v>
       </c>
-      <c r="B181" t="s">
-        <v>365</v>
+      <c r="B181" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="C181">
         <v>100000</v>
@@ -5849,18 +5851,18 @@
         <v>98000</v>
       </c>
       <c r="E181" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F181" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>180</v>
       </c>
-      <c r="B182" t="s">
-        <v>367</v>
+      <c r="B182" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="C182">
         <v>100000</v>
@@ -5869,18 +5871,18 @@
         <v>98000</v>
       </c>
       <c r="E182" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F182" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>181</v>
       </c>
-      <c r="B183" t="s">
-        <v>369</v>
+      <c r="B183" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="C183">
         <v>63000</v>
@@ -5889,18 +5891,18 @@
         <v>61740</v>
       </c>
       <c r="E183" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F183" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>182</v>
       </c>
-      <c r="B184" t="s">
-        <v>371</v>
+      <c r="B184" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="C184">
         <v>100000</v>
@@ -5909,18 +5911,18 @@
         <v>98000</v>
       </c>
       <c r="E184" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F184" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>183</v>
       </c>
-      <c r="B185" t="s">
-        <v>373</v>
+      <c r="B185" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="C185">
         <v>100000</v>
@@ -5929,18 +5931,18 @@
         <v>98000</v>
       </c>
       <c r="E185" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F185" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>184</v>
       </c>
-      <c r="B186" t="s">
-        <v>375</v>
+      <c r="B186" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="C186">
         <v>60000</v>
@@ -5949,18 +5951,18 @@
         <v>58800</v>
       </c>
       <c r="E186" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F186" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>185</v>
       </c>
-      <c r="B187" t="s">
-        <v>377</v>
+      <c r="B187" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="C187">
         <v>44000</v>
@@ -5969,18 +5971,18 @@
         <v>43120</v>
       </c>
       <c r="E187" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F187" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>186</v>
       </c>
-      <c r="B188" t="s">
-        <v>379</v>
+      <c r="B188" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="C188">
         <v>110000</v>
@@ -5989,18 +5991,18 @@
         <v>107800</v>
       </c>
       <c r="E188" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F188" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>187</v>
       </c>
-      <c r="B189" t="s">
-        <v>381</v>
+      <c r="B189" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="C189">
         <v>50000</v>
@@ -6009,18 +6011,18 @@
         <v>49000</v>
       </c>
       <c r="E189" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F189" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>188</v>
       </c>
-      <c r="B190" t="s">
-        <v>383</v>
+      <c r="B190" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="C190">
         <v>300000</v>
@@ -6029,18 +6031,18 @@
         <v>294000</v>
       </c>
       <c r="E190" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F190" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>189</v>
       </c>
-      <c r="B191" t="s">
-        <v>385</v>
+      <c r="B191" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="C191">
         <v>100000</v>
@@ -6049,18 +6051,18 @@
         <v>98000</v>
       </c>
       <c r="E191" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F191" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>190</v>
       </c>
-      <c r="B192" t="s">
-        <v>387</v>
+      <c r="B192" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="C192">
         <v>79000</v>
@@ -6069,18 +6071,18 @@
         <v>77420</v>
       </c>
       <c r="E192" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F192" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>191</v>
       </c>
-      <c r="B193" t="s">
-        <v>389</v>
+      <c r="B193" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="C193">
         <v>300000</v>
@@ -6089,18 +6091,18 @@
         <v>294000</v>
       </c>
       <c r="E193" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F193" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>192</v>
       </c>
-      <c r="B194" t="s">
-        <v>391</v>
+      <c r="B194" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="C194">
         <v>100000</v>
@@ -6109,18 +6111,18 @@
         <v>98000</v>
       </c>
       <c r="E194" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F194" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>193</v>
       </c>
-      <c r="B195" t="s">
-        <v>393</v>
+      <c r="B195" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="C195">
         <v>100000</v>
@@ -6129,18 +6131,18 @@
         <v>98000</v>
       </c>
       <c r="E195" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F195" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>194</v>
       </c>
-      <c r="B196" t="s">
-        <v>395</v>
+      <c r="B196" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="C196">
         <v>51010</v>
@@ -6149,18 +6151,18 @@
         <v>49989.8</v>
       </c>
       <c r="E196" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F196" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>195</v>
       </c>
-      <c r="B197" t="s">
-        <v>397</v>
+      <c r="B197" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="C197">
         <v>102000</v>
@@ -6169,18 +6171,18 @@
         <v>99960</v>
       </c>
       <c r="E197" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F197" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>196</v>
       </c>
-      <c r="B198" t="s">
-        <v>399</v>
+      <c r="B198" s="2" t="s">
+        <v>395</v>
       </c>
       <c r="C198">
         <v>200000</v>
@@ -6189,18 +6191,18 @@
         <v>196000</v>
       </c>
       <c r="E198" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F198" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>197</v>
       </c>
-      <c r="B199" t="s">
-        <v>401</v>
+      <c r="B199" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="C199">
         <v>100000</v>
@@ -6209,18 +6211,18 @@
         <v>98000</v>
       </c>
       <c r="E199" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F199" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>198</v>
       </c>
-      <c r="B200" t="s">
-        <v>403</v>
+      <c r="B200" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="C200">
         <v>69000</v>
@@ -6229,18 +6231,18 @@
         <v>67620</v>
       </c>
       <c r="E200" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F200" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>199</v>
       </c>
-      <c r="B201" t="s">
-        <v>405</v>
+      <c r="B201" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="C201">
         <v>100000</v>
@@ -6249,18 +6251,18 @@
         <v>98000</v>
       </c>
       <c r="E201" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F201" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>200</v>
       </c>
-      <c r="B202" t="s">
-        <v>407</v>
+      <c r="B202" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="C202">
         <v>49000</v>
@@ -6269,18 +6271,18 @@
         <v>48020</v>
       </c>
       <c r="E202" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F202" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>201</v>
       </c>
-      <c r="B203" t="s">
-        <v>409</v>
+      <c r="B203" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="C203">
         <v>66800</v>
@@ -6289,18 +6291,18 @@
         <v>65464</v>
       </c>
       <c r="E203" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F203" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>202</v>
       </c>
-      <c r="B204" t="s">
-        <v>411</v>
+      <c r="B204" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="C204">
         <v>51000</v>
@@ -6309,18 +6311,18 @@
         <v>49980</v>
       </c>
       <c r="E204" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F204" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>203</v>
       </c>
-      <c r="B205" t="s">
-        <v>413</v>
+      <c r="B205" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="C205">
         <v>112000</v>
@@ -6329,18 +6331,18 @@
         <v>109760</v>
       </c>
       <c r="E205" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F205" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>204</v>
       </c>
-      <c r="B206" t="s">
-        <v>415</v>
+      <c r="B206" s="2" t="s">
+        <v>411</v>
       </c>
       <c r="C206">
         <v>170000</v>
@@ -6349,18 +6351,18 @@
         <v>166600</v>
       </c>
       <c r="E206" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F206" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>205</v>
       </c>
-      <c r="B207" t="s">
-        <v>417</v>
+      <c r="B207" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="C207">
         <v>100000</v>
@@ -6369,18 +6371,18 @@
         <v>98000</v>
       </c>
       <c r="E207" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F207" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>206</v>
       </c>
-      <c r="B208" t="s">
-        <v>419</v>
+      <c r="B208" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="C208">
         <v>84460</v>
@@ -6389,18 +6391,18 @@
         <v>82770.8</v>
       </c>
       <c r="E208" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F208" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>207</v>
       </c>
-      <c r="B209" t="s">
-        <v>421</v>
+      <c r="B209" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="C209">
         <v>250000</v>
@@ -6409,18 +6411,18 @@
         <v>245000</v>
       </c>
       <c r="E209" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F209" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>208</v>
       </c>
-      <c r="B210" t="s">
-        <v>423</v>
+      <c r="B210" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="C210">
         <v>268000</v>
@@ -6429,18 +6431,18 @@
         <v>262640</v>
       </c>
       <c r="E210" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F210" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>209</v>
       </c>
-      <c r="B211" t="s">
-        <v>425</v>
+      <c r="B211" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="C211">
         <v>34000</v>
@@ -6449,18 +6451,18 @@
         <v>33320</v>
       </c>
       <c r="E211" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F211" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>210</v>
       </c>
-      <c r="B212" t="s">
-        <v>427</v>
+      <c r="B212" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="C212">
         <v>134000</v>
@@ -6469,18 +6471,18 @@
         <v>131320</v>
       </c>
       <c r="E212" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F212" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>211</v>
       </c>
-      <c r="B213" t="s">
-        <v>429</v>
+      <c r="B213" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="C213">
         <v>200000</v>
@@ -6489,18 +6491,18 @@
         <v>196000</v>
       </c>
       <c r="E213" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F213" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>212</v>
       </c>
-      <c r="B214" t="s">
-        <v>431</v>
+      <c r="B214" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="C214">
         <v>69000</v>
@@ -6509,18 +6511,18 @@
         <v>67620</v>
       </c>
       <c r="E214" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F214" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>213</v>
       </c>
-      <c r="B215" t="s">
-        <v>433</v>
+      <c r="B215" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="C215">
         <v>62000</v>
@@ -6529,18 +6531,18 @@
         <v>60760</v>
       </c>
       <c r="E215" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F215" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>214</v>
       </c>
-      <c r="B216" t="s">
-        <v>435</v>
+      <c r="B216" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="C216">
         <v>26000</v>
@@ -6549,18 +6551,18 @@
         <v>25480</v>
       </c>
       <c r="E216" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F216" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>215</v>
       </c>
-      <c r="B217" t="s">
-        <v>438</v>
+      <c r="B217" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="C217">
         <v>108000</v>
@@ -6569,18 +6571,18 @@
         <v>105840</v>
       </c>
       <c r="E217" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F217" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>216</v>
       </c>
-      <c r="B218" t="s">
-        <v>440</v>
+      <c r="B218" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="C218">
         <v>150000</v>
@@ -6589,18 +6591,18 @@
         <v>147000</v>
       </c>
       <c r="E218" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F218" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>217</v>
       </c>
-      <c r="B219" t="s">
-        <v>442</v>
+      <c r="B219" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="C219">
         <v>70000</v>
@@ -6609,18 +6611,18 @@
         <v>68600</v>
       </c>
       <c r="E219" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F219" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>218</v>
       </c>
-      <c r="B220" t="s">
-        <v>444</v>
+      <c r="B220" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="C220">
         <v>224000</v>
@@ -6629,18 +6631,18 @@
         <v>219520</v>
       </c>
       <c r="E220" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F220" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>219</v>
       </c>
-      <c r="B221" t="s">
-        <v>446</v>
+      <c r="B221" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="C221">
         <v>200000</v>
@@ -6649,18 +6651,18 @@
         <v>196000</v>
       </c>
       <c r="E221" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F221" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>220</v>
       </c>
-      <c r="B222" t="s">
-        <v>448</v>
+      <c r="B222" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="C222">
         <v>88000</v>
@@ -6669,18 +6671,18 @@
         <v>86240</v>
       </c>
       <c r="E222" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F222" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>221</v>
       </c>
-      <c r="B223" t="s">
-        <v>450</v>
+      <c r="B223" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="C223">
         <v>100000</v>
@@ -6689,18 +6691,18 @@
         <v>98000</v>
       </c>
       <c r="E223" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F223" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>222</v>
       </c>
-      <c r="B224" t="s">
-        <v>452</v>
+      <c r="B224" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="C224">
         <v>26000</v>
@@ -6709,18 +6711,18 @@
         <v>25480</v>
       </c>
       <c r="E224" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F224" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>223</v>
       </c>
-      <c r="B225" t="s">
-        <v>454</v>
+      <c r="B225" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="C225">
         <v>200000</v>
@@ -6729,18 +6731,18 @@
         <v>196000</v>
       </c>
       <c r="E225" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F225" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>224</v>
       </c>
-      <c r="B226" t="s">
-        <v>456</v>
+      <c r="B226" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="C226">
         <v>60000</v>
@@ -6749,18 +6751,18 @@
         <v>58800</v>
       </c>
       <c r="E226" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F226" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>225</v>
       </c>
-      <c r="B227" t="s">
-        <v>458</v>
+      <c r="B227" s="2" t="s">
+        <v>454</v>
       </c>
       <c r="C227">
         <v>110000</v>
@@ -6769,18 +6771,18 @@
         <v>107800</v>
       </c>
       <c r="E227" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F227" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>226</v>
       </c>
-      <c r="B228" t="s">
-        <v>460</v>
+      <c r="B228" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="C228">
         <v>140000</v>
@@ -6789,18 +6791,18 @@
         <v>137200</v>
       </c>
       <c r="E228" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F228" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>227</v>
       </c>
-      <c r="B229" t="s">
-        <v>462</v>
+      <c r="B229" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="C229">
         <v>20000</v>
@@ -6809,18 +6811,18 @@
         <v>19600</v>
       </c>
       <c r="E229" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F229" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>228</v>
       </c>
-      <c r="B230" t="s">
-        <v>464</v>
+      <c r="B230" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="C230">
         <v>48000</v>
@@ -6829,18 +6831,18 @@
         <v>47040</v>
       </c>
       <c r="E230" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F230" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>229</v>
       </c>
-      <c r="B231" t="s">
-        <v>466</v>
+      <c r="B231" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="C231">
         <v>79000</v>
@@ -6849,18 +6851,18 @@
         <v>77420</v>
       </c>
       <c r="E231" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F231" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>230</v>
       </c>
-      <c r="B232" t="s">
-        <v>468</v>
+      <c r="B232" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="C232">
         <v>48000</v>
@@ -6869,18 +6871,18 @@
         <v>47040</v>
       </c>
       <c r="E232" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F232" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>231</v>
       </c>
-      <c r="B233" t="s">
-        <v>470</v>
+      <c r="B233" s="2" t="s">
+        <v>466</v>
       </c>
       <c r="C233">
         <v>200000</v>
@@ -6889,18 +6891,18 @@
         <v>196000</v>
       </c>
       <c r="E233" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F233" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>232</v>
       </c>
-      <c r="B234" t="s">
-        <v>472</v>
+      <c r="B234" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="C234">
         <v>200000</v>
@@ -6909,18 +6911,18 @@
         <v>196000</v>
       </c>
       <c r="E234" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F234" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>233</v>
       </c>
-      <c r="B235" t="s">
-        <v>474</v>
+      <c r="B235" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="C235">
         <v>112000</v>
@@ -6929,18 +6931,18 @@
         <v>109760</v>
       </c>
       <c r="E235" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F235" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>234</v>
       </c>
-      <c r="B236" t="s">
-        <v>476</v>
+      <c r="B236" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="C236">
         <v>99180</v>
@@ -6949,18 +6951,18 @@
         <v>97196.4</v>
       </c>
       <c r="E236" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F236" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>235</v>
       </c>
-      <c r="B237" t="s">
-        <v>478</v>
+      <c r="B237" s="2" t="s">
+        <v>474</v>
       </c>
       <c r="C237">
         <v>65000</v>
@@ -6969,18 +6971,18 @@
         <v>63700</v>
       </c>
       <c r="E237" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F237" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>236</v>
       </c>
-      <c r="B238" t="s">
-        <v>480</v>
+      <c r="B238" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="C238">
         <v>200000</v>
@@ -6989,18 +6991,18 @@
         <v>196000</v>
       </c>
       <c r="E238" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F238" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>237</v>
       </c>
-      <c r="B239" t="s">
-        <v>482</v>
+      <c r="B239" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="C239">
         <v>100000</v>
@@ -7009,18 +7011,18 @@
         <v>98000</v>
       </c>
       <c r="E239" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F239" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>238</v>
       </c>
-      <c r="B240" t="s">
-        <v>484</v>
+      <c r="B240" s="2" t="s">
+        <v>480</v>
       </c>
       <c r="C240">
         <v>69120</v>
@@ -7029,18 +7031,18 @@
         <v>67737.600000000006</v>
       </c>
       <c r="E240" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F240" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>239</v>
       </c>
-      <c r="B241" t="s">
-        <v>486</v>
+      <c r="B241" s="2" t="s">
+        <v>482</v>
       </c>
       <c r="C241">
         <v>100000</v>
@@ -7049,18 +7051,18 @@
         <v>98000</v>
       </c>
       <c r="E241" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F241" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>240</v>
       </c>
-      <c r="B242" t="s">
-        <v>488</v>
+      <c r="B242" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="C242">
         <v>200000</v>
@@ -7069,18 +7071,18 @@
         <v>196000</v>
       </c>
       <c r="E242" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F242" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>241</v>
       </c>
-      <c r="B243" t="s">
-        <v>490</v>
+      <c r="B243" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="C243">
         <v>44000</v>
@@ -7089,18 +7091,18 @@
         <v>43120</v>
       </c>
       <c r="E243" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F243" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>242</v>
       </c>
-      <c r="B244" t="s">
-        <v>492</v>
+      <c r="B244" s="2" t="s">
+        <v>488</v>
       </c>
       <c r="C244">
         <v>26000</v>
@@ -7109,18 +7111,18 @@
         <v>25480</v>
       </c>
       <c r="E244" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F244" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>243</v>
       </c>
-      <c r="B245" t="s">
-        <v>494</v>
+      <c r="B245" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="C245">
         <v>50000</v>
@@ -7129,18 +7131,18 @@
         <v>49000</v>
       </c>
       <c r="E245" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F245" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>244</v>
       </c>
-      <c r="B246" t="s">
-        <v>496</v>
+      <c r="B246" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="C246">
         <v>80000</v>
@@ -7149,18 +7151,18 @@
         <v>78400</v>
       </c>
       <c r="E246" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F246" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>245</v>
       </c>
-      <c r="B247" t="s">
-        <v>498</v>
+      <c r="B247" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="C247">
         <v>280000</v>
@@ -7169,18 +7171,18 @@
         <v>274400</v>
       </c>
       <c r="E247" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F247" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>246</v>
       </c>
-      <c r="B248" t="s">
-        <v>501</v>
+      <c r="B248" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="C248">
         <v>64000</v>
@@ -7189,18 +7191,18 @@
         <v>62720</v>
       </c>
       <c r="E248" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F248" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>247</v>
       </c>
-      <c r="B249" t="s">
-        <v>503</v>
+      <c r="B249" s="2" t="s">
+        <v>499</v>
       </c>
       <c r="C249">
         <v>200000</v>
@@ -7209,18 +7211,18 @@
         <v>196000</v>
       </c>
       <c r="E249" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F249" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>248</v>
       </c>
-      <c r="B250" t="s">
-        <v>505</v>
+      <c r="B250" s="2" t="s">
+        <v>501</v>
       </c>
       <c r="C250">
         <v>349000</v>
@@ -7229,18 +7231,18 @@
         <v>342020</v>
       </c>
       <c r="E250" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F250" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>249</v>
       </c>
-      <c r="B251" t="s">
-        <v>507</v>
+      <c r="B251" s="2" t="s">
+        <v>503</v>
       </c>
       <c r="C251">
         <v>280000</v>
@@ -7249,18 +7251,18 @@
         <v>274400</v>
       </c>
       <c r="E251" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F251" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>250</v>
       </c>
-      <c r="B252" t="s">
-        <v>509</v>
+      <c r="B252" s="2" t="s">
+        <v>505</v>
       </c>
       <c r="C252">
         <v>280000</v>
@@ -7269,18 +7271,18 @@
         <v>274400</v>
       </c>
       <c r="E252" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F252" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>251</v>
       </c>
-      <c r="B253" t="s">
-        <v>511</v>
+      <c r="B253" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="C253">
         <v>200000</v>
@@ -7289,18 +7291,18 @@
         <v>196000</v>
       </c>
       <c r="E253" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F253" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>252</v>
       </c>
-      <c r="B254" t="s">
-        <v>513</v>
+      <c r="B254" s="2" t="s">
+        <v>509</v>
       </c>
       <c r="C254">
         <v>150000</v>
@@ -7309,18 +7311,18 @@
         <v>147000</v>
       </c>
       <c r="E254" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F254" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>253</v>
       </c>
-      <c r="B255" t="s">
-        <v>515</v>
+      <c r="B255" s="2" t="s">
+        <v>511</v>
       </c>
       <c r="C255">
         <v>1790000</v>
@@ -7329,18 +7331,18 @@
         <v>1754200</v>
       </c>
       <c r="E255" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F255" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>254</v>
       </c>
-      <c r="B256" t="s">
-        <v>517</v>
+      <c r="B256" s="2" t="s">
+        <v>513</v>
       </c>
       <c r="C256">
         <v>34000</v>
@@ -7349,18 +7351,18 @@
         <v>33320</v>
       </c>
       <c r="E256" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F256" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>255</v>
       </c>
-      <c r="B257" t="s">
-        <v>519</v>
+      <c r="B257" s="2" t="s">
+        <v>515</v>
       </c>
       <c r="C257">
         <v>88000</v>
@@ -7369,18 +7371,18 @@
         <v>86240</v>
       </c>
       <c r="E257" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F257" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>256</v>
       </c>
-      <c r="B258" t="s">
-        <v>521</v>
+      <c r="B258" s="2" t="s">
+        <v>517</v>
       </c>
       <c r="C258">
         <v>200000</v>
@@ -7389,18 +7391,18 @@
         <v>196000</v>
       </c>
       <c r="E258" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F258" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>257</v>
       </c>
-      <c r="B259" t="s">
-        <v>523</v>
+      <c r="B259" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="C259">
         <v>60000</v>
@@ -7409,18 +7411,18 @@
         <v>58800</v>
       </c>
       <c r="E259" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F259" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>258</v>
       </c>
-      <c r="B260" t="s">
-        <v>525</v>
+      <c r="B260" s="2" t="s">
+        <v>521</v>
       </c>
       <c r="C260">
         <v>208000</v>
@@ -7429,18 +7431,18 @@
         <v>203840</v>
       </c>
       <c r="E260" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F260" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>259</v>
       </c>
-      <c r="B261" t="s">
-        <v>527</v>
+      <c r="B261" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="C261">
         <v>116000</v>
@@ -7449,18 +7451,18 @@
         <v>113680</v>
       </c>
       <c r="E261" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F261" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>260</v>
       </c>
-      <c r="B262" t="s">
-        <v>529</v>
+      <c r="B262" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="C262">
         <v>100000</v>
@@ -7469,18 +7471,18 @@
         <v>98000</v>
       </c>
       <c r="E262" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F262" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>261</v>
       </c>
-      <c r="B263" t="s">
-        <v>531</v>
+      <c r="B263" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="C263">
         <v>230000</v>
@@ -7489,18 +7491,18 @@
         <v>225400</v>
       </c>
       <c r="E263" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F263" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>262</v>
       </c>
-      <c r="B264" t="s">
-        <v>533</v>
+      <c r="B264" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="C264">
         <v>212000</v>
@@ -7509,18 +7511,18 @@
         <v>207760</v>
       </c>
       <c r="E264" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F264" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>263</v>
       </c>
-      <c r="B265" t="s">
-        <v>535</v>
+      <c r="B265" s="2" t="s">
+        <v>531</v>
       </c>
       <c r="C265">
         <v>280000</v>
@@ -7529,18 +7531,18 @@
         <v>274400</v>
       </c>
       <c r="E265" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F265" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>264</v>
       </c>
-      <c r="B266" t="s">
-        <v>537</v>
+      <c r="B266" s="2" t="s">
+        <v>533</v>
       </c>
       <c r="C266">
         <v>31000</v>
@@ -7549,18 +7551,18 @@
         <v>30380</v>
       </c>
       <c r="E266" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F266" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>265</v>
       </c>
-      <c r="B267" t="s">
-        <v>539</v>
+      <c r="B267" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="C267">
         <v>31000</v>
@@ -7569,18 +7571,18 @@
         <v>30380</v>
       </c>
       <c r="E267" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F267" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>266</v>
       </c>
-      <c r="B268" t="s">
-        <v>541</v>
+      <c r="B268" s="2" t="s">
+        <v>537</v>
       </c>
       <c r="C268">
         <v>118000</v>
@@ -7589,18 +7591,18 @@
         <v>115640</v>
       </c>
       <c r="E268" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F268" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>267</v>
       </c>
-      <c r="B269" t="s">
-        <v>543</v>
+      <c r="B269" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="C269">
         <v>200000</v>
@@ -7609,18 +7611,18 @@
         <v>196000</v>
       </c>
       <c r="E269" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="F269" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>268</v>
       </c>
-      <c r="B270" t="s">
-        <v>545</v>
+      <c r="B270" s="2" t="s">
+        <v>541</v>
       </c>
       <c r="C270">
         <v>69120</v>
@@ -7629,18 +7631,18 @@
         <v>67737.600000000006</v>
       </c>
       <c r="E270" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F270" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>269</v>
       </c>
-      <c r="B271" t="s">
-        <v>547</v>
+      <c r="B271" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="C271">
         <v>100000</v>
@@ -7649,18 +7651,18 @@
         <v>98000</v>
       </c>
       <c r="E271" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F271" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>270</v>
       </c>
-      <c r="B272" t="s">
-        <v>549</v>
+      <c r="B272" s="2" t="s">
+        <v>545</v>
       </c>
       <c r="C272">
         <v>325000</v>
@@ -7669,18 +7671,18 @@
         <v>318500</v>
       </c>
       <c r="E272" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F272" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>271</v>
       </c>
-      <c r="B273" t="s">
-        <v>551</v>
+      <c r="B273" s="2" t="s">
+        <v>547</v>
       </c>
       <c r="C273">
         <v>48000</v>
@@ -7689,18 +7691,18 @@
         <v>47040</v>
       </c>
       <c r="E273" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F273" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>272</v>
       </c>
-      <c r="B274" t="s">
-        <v>553</v>
+      <c r="B274" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="C274">
         <v>265000</v>
@@ -7709,18 +7711,18 @@
         <v>259700</v>
       </c>
       <c r="E274" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F274" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>273</v>
       </c>
-      <c r="B275" t="s">
-        <v>555</v>
+      <c r="B275" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="C275">
         <v>300000</v>
@@ -7729,18 +7731,18 @@
         <v>294000</v>
       </c>
       <c r="E275" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F275" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>274</v>
       </c>
-      <c r="B276" t="s">
-        <v>557</v>
+      <c r="B276" s="2" t="s">
+        <v>553</v>
       </c>
       <c r="C276">
         <v>48000</v>
@@ -7749,18 +7751,18 @@
         <v>47040</v>
       </c>
       <c r="E276" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F276" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>275</v>
       </c>
-      <c r="B277" t="s">
-        <v>559</v>
+      <c r="B277" s="2" t="s">
+        <v>555</v>
       </c>
       <c r="C277">
         <v>112000</v>
@@ -7769,18 +7771,18 @@
         <v>109760</v>
       </c>
       <c r="E277" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F277" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>276</v>
       </c>
-      <c r="B278" t="s">
-        <v>561</v>
+      <c r="B278" s="2" t="s">
+        <v>557</v>
       </c>
       <c r="C278">
         <v>17000</v>
@@ -7789,18 +7791,18 @@
         <v>16660</v>
       </c>
       <c r="E278" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="F278" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>277</v>
       </c>
-      <c r="B279" t="s">
-        <v>563</v>
+      <c r="B279" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="C279">
         <v>150000</v>
@@ -7809,18 +7811,18 @@
         <v>147000</v>
       </c>
       <c r="E279" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F279" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>278</v>
       </c>
-      <c r="B280" t="s">
-        <v>565</v>
+      <c r="B280" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="C280">
         <v>150000</v>
@@ -7829,18 +7831,18 @@
         <v>147000</v>
       </c>
       <c r="E280" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F280" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>279</v>
       </c>
-      <c r="B281" t="s">
-        <v>567</v>
+      <c r="B281" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="C281">
         <v>110000</v>
@@ -7849,18 +7851,18 @@
         <v>107800</v>
       </c>
       <c r="E281" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F281" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>280</v>
       </c>
-      <c r="B282" t="s">
-        <v>569</v>
+      <c r="B282" s="2" t="s">
+        <v>565</v>
       </c>
       <c r="C282">
         <v>100000</v>
@@ -7869,18 +7871,18 @@
         <v>98000</v>
       </c>
       <c r="E282" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F282" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>281</v>
       </c>
-      <c r="B283" t="s">
-        <v>571</v>
+      <c r="B283" s="2" t="s">
+        <v>567</v>
       </c>
       <c r="C283">
         <v>100000</v>
@@ -7889,18 +7891,18 @@
         <v>98000</v>
       </c>
       <c r="E283" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F283" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>282</v>
       </c>
-      <c r="B284" t="s">
-        <v>573</v>
+      <c r="B284" s="2" t="s">
+        <v>569</v>
       </c>
       <c r="C284">
         <v>102000</v>
@@ -7909,18 +7911,18 @@
         <v>99960</v>
       </c>
       <c r="E284" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F284" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>283</v>
       </c>
-      <c r="B285" t="s">
-        <v>575</v>
+      <c r="B285" s="2" t="s">
+        <v>571</v>
       </c>
       <c r="C285">
         <v>69120</v>
@@ -7929,18 +7931,18 @@
         <v>67737.600000000006</v>
       </c>
       <c r="E285" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F285" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>284</v>
       </c>
-      <c r="B286" t="s">
-        <v>577</v>
+      <c r="B286" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="C286">
         <v>170000</v>
@@ -7949,18 +7951,18 @@
         <v>166600</v>
       </c>
       <c r="E286" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F286" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>285</v>
       </c>
-      <c r="B287" t="s">
-        <v>579</v>
+      <c r="B287" s="2" t="s">
+        <v>575</v>
       </c>
       <c r="C287">
         <v>45000</v>
@@ -7969,18 +7971,18 @@
         <v>44100</v>
       </c>
       <c r="E287" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F287" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>286</v>
       </c>
-      <c r="B288" t="s">
-        <v>581</v>
+      <c r="B288" s="2" t="s">
+        <v>577</v>
       </c>
       <c r="C288">
         <v>150000</v>
@@ -7989,18 +7991,18 @@
         <v>147000</v>
       </c>
       <c r="E288" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F288" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>287</v>
       </c>
-      <c r="B289" t="s">
-        <v>583</v>
+      <c r="B289" s="2" t="s">
+        <v>579</v>
       </c>
       <c r="C289">
         <v>150000</v>
@@ -8009,18 +8011,18 @@
         <v>147000</v>
       </c>
       <c r="E289" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F289" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>288</v>
       </c>
-      <c r="B290" t="s">
-        <v>585</v>
+      <c r="B290" s="2" t="s">
+        <v>581</v>
       </c>
       <c r="C290">
         <v>60000</v>
@@ -8029,18 +8031,18 @@
         <v>58800</v>
       </c>
       <c r="E290" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F290" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>289</v>
       </c>
-      <c r="B291" t="s">
-        <v>587</v>
+      <c r="B291" s="2" t="s">
+        <v>583</v>
       </c>
       <c r="C291">
         <v>210000</v>
@@ -8049,18 +8051,18 @@
         <v>205800</v>
       </c>
       <c r="E291" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F291" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>290</v>
       </c>
-      <c r="B292" t="s">
-        <v>589</v>
+      <c r="B292" s="2" t="s">
+        <v>585</v>
       </c>
       <c r="C292">
         <v>175000</v>
@@ -8069,18 +8071,18 @@
         <v>171500</v>
       </c>
       <c r="E292" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F292" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>291</v>
       </c>
-      <c r="B293" t="s">
-        <v>591</v>
+      <c r="B293" s="2" t="s">
+        <v>587</v>
       </c>
       <c r="C293">
         <v>280000</v>
@@ -8089,18 +8091,18 @@
         <v>274400</v>
       </c>
       <c r="E293" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F293" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>292</v>
       </c>
-      <c r="B294" t="s">
-        <v>593</v>
+      <c r="B294" s="2" t="s">
+        <v>589</v>
       </c>
       <c r="C294">
         <v>74000</v>
@@ -8109,18 +8111,18 @@
         <v>72520</v>
       </c>
       <c r="E294" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F294" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>293</v>
       </c>
-      <c r="B295" t="s">
-        <v>595</v>
+      <c r="B295" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="C295">
         <v>44000</v>
@@ -8129,18 +8131,18 @@
         <v>43120</v>
       </c>
       <c r="E295" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F295" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>294</v>
       </c>
-      <c r="B296" t="s">
-        <v>597</v>
+      <c r="B296" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="C296">
         <v>70000</v>
@@ -8149,18 +8151,18 @@
         <v>68600</v>
       </c>
       <c r="E296" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="F296" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>295</v>
       </c>
-      <c r="B297" t="s">
-        <v>599</v>
+      <c r="B297" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="C297">
         <v>27000</v>
@@ -8169,18 +8171,18 @@
         <v>26460</v>
       </c>
       <c r="E297" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F297" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>296</v>
       </c>
-      <c r="B298" t="s">
-        <v>601</v>
+      <c r="B298" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="C298">
         <v>118000</v>
@@ -8189,18 +8191,18 @@
         <v>115640</v>
       </c>
       <c r="E298" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="F298" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>297</v>
       </c>
-      <c r="B299" t="s">
-        <v>603</v>
+      <c r="B299" s="2" t="s">
+        <v>599</v>
       </c>
       <c r="C299">
         <v>49000</v>
@@ -8209,18 +8211,18 @@
         <v>48020</v>
       </c>
       <c r="E299" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F299" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>298</v>
       </c>
-      <c r="B300" t="s">
-        <v>605</v>
+      <c r="B300" s="2" t="s">
+        <v>601</v>
       </c>
       <c r="C300">
         <v>87000</v>
@@ -8229,18 +8231,18 @@
         <v>85260</v>
       </c>
       <c r="E300" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F300" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>299</v>
       </c>
-      <c r="B301" t="s">
-        <v>607</v>
+      <c r="B301" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="C301">
         <v>27000</v>
@@ -8249,18 +8251,18 @@
         <v>26460</v>
       </c>
       <c r="E301" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F301" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>300</v>
       </c>
-      <c r="B302" t="s">
-        <v>609</v>
+      <c r="B302" s="2" t="s">
+        <v>605</v>
       </c>
       <c r="C302">
         <v>27000</v>
@@ -8269,10 +8271,10 @@
         <v>26460</v>
       </c>
       <c r="E302" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="F302" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
